--- a/tests/workbooktests/workbooks/test_piecewiseyieldcurve.xlsx
+++ b/tests/workbooktests/workbooks/test_piecewiseyieldcurve.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB5F203-C7B9-47D1-A18D-24B1A403E578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D005E5-7915-46F3-BF71-E636FF58A7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{86257255-1BE2-4D8D-B157-4C7713C56C65}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{86257255-1BE2-4D8D-B157-4C7713C56C65}"/>
   </bookViews>
   <sheets>
     <sheet name="PiecewiseYieldCurve" sheetId="1" r:id="rId1"/>
@@ -21428,8 +21428,8 @@
         <v>2</v>
       </c>
       <c r="B4" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlEonia()</f>
-        <v>欣[test_piecewiseyieldcurve.xlsx]PiecewiseYieldCurve!R4C2Eonia,A</v>
+        <f t="array" ref="B4">_xll.qlEonia(,B2)</f>
+        <v>欣[test_piecewiseyieldcurve.xlsx]PiecewiseYieldCurve!R4C2Eonia,G</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -21437,8 +21437,8 @@
         <v>3</v>
       </c>
       <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlEuribor("6m")</f>
-        <v>欣[test_piecewiseyieldcurve.xlsx]PiecewiseYieldCurve!R5C2Euribor,A</v>
+        <f t="array" ref="B5">_xll.qlEuribor("6m",,B2)</f>
+        <v>欣[test_piecewiseyieldcurve.xlsx]PiecewiseYieldCurve!R5C2Euribor,G</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -22014,7 +22014,7 @@
         <v>33</v>
       </c>
       <c r="B65" s="1" cm="1">
-        <f t="array" ref="B65">_xll.qlCalendarAdvance2($B$7,$B$2,A65)</f>
+        <f t="array" ref="B65">_xll.qlCalendarAdvance($B$7,$B$2,A65)</f>
         <v>46722</v>
       </c>
       <c r="C65">
@@ -22030,7 +22030,7 @@
         <v>34</v>
       </c>
       <c r="B66" s="1" cm="1">
-        <f t="array" ref="B66">_xll.qlCalendarAdvance2($B$7,$B$2,A66)</f>
+        <f t="array" ref="B66">_xll.qlCalendarAdvance($B$7,$B$2,A66)</f>
         <v>47088</v>
       </c>
       <c r="C66">
@@ -42252,7 +42252,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlEonia()</f>
+        <f t="array" ref="B4">_xll.qlEonia(,B2)</f>
         <v>欣[test_piecewiseyieldcurve.xlsx]PiecewiseSpreadYieldCurve!R4C2Eonia,A</v>
       </c>
     </row>
@@ -42261,8 +42261,8 @@
         <v>3</v>
       </c>
       <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlEuribor("6m")</f>
-        <v>欣[test_piecewiseyieldcurve.xlsx]PiecewiseSpreadYieldCurve!R5C2Euribor,A</v>
+        <f t="array" ref="B5">_xll.qlEuribor("6m",,B2)</f>
+        <v>欣[test_piecewiseyieldcurve.xlsx]PiecewiseSpreadYieldCurve!R5C2Euribor,I</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
